--- a/NECP Scenario/Results/Regional Results/EL61_Generation.xlsx
+++ b/NECP Scenario/Results/Regional Results/EL61_Generation.xlsx
@@ -537,25 +537,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.547327677525482E-12</v>
+        <v>2.284568465929077E-12</v>
       </c>
       <c r="C2">
-        <v>8.102411183979526E-13</v>
+        <v>1.196287547155383E-12</v>
       </c>
       <c r="D2">
-        <v>1.190478139949388E-12</v>
+        <v>1.757695533675045E-12</v>
       </c>
       <c r="E2">
-        <v>1.749240319653396E-12</v>
+        <v>2.582687816586751E-12</v>
       </c>
       <c r="F2">
-        <v>2.570234640297012E-12</v>
+        <v>3.794852679390653E-12</v>
       </c>
       <c r="G2">
-        <v>3.776474989063023E-12</v>
+        <v>5.575820524275753E-12</v>
       </c>
       <c r="H2">
-        <v>2.28878682774283E-11</v>
+        <v>3.379324138070518E-11</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -563,25 +563,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>6.487124046304973E-08</v>
+        <v>9.319230339476127E-08</v>
       </c>
       <c r="C3">
-        <v>6.872449185798485E-08</v>
+        <v>9.85833065848553E-08</v>
       </c>
       <c r="D3">
-        <v>2.6684512131803E-07</v>
+        <v>3.967612850526673E-07</v>
       </c>
       <c r="E3">
-        <v>8.308559095985626E-07</v>
+        <v>1.08190507560059E-06</v>
       </c>
       <c r="F3">
-        <v>0.244597688331536</v>
+        <v>0.2324709132865126</v>
       </c>
       <c r="G3">
-        <v>0.5782943096379326</v>
+        <v>0.7495705593024111</v>
       </c>
       <c r="H3">
-        <v>1.06903551112808</v>
+        <v>0.9716040250798694</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +589,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>5.51405543959448E-08</v>
+        <v>7.921345788754525E-08</v>
       </c>
       <c r="C4">
-        <v>5.841581808577984E-08</v>
+        <v>8.379581060153146E-08</v>
       </c>
       <c r="D4">
-        <v>2.268183531268494E-07</v>
+        <v>3.372470922991935E-07</v>
       </c>
       <c r="E4">
-        <v>7.062275231653783E-07</v>
+        <v>9.196193142650131E-07</v>
       </c>
       <c r="F4">
-        <v>0.2079080350817763</v>
+        <v>0.1976002762935102</v>
       </c>
       <c r="G4">
-        <v>0.4915501631931021</v>
+        <v>0.6371349754070024</v>
       </c>
       <c r="H4">
-        <v>0.9086801844586302</v>
+        <v>0.8258634213179404</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -618,22 +618,22 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>5.974759585081446E-08</v>
+        <v>9.188578913561411E-08</v>
       </c>
       <c r="D5">
-        <v>1.916536571495187E-07</v>
+        <v>3.258646575253684E-07</v>
       </c>
       <c r="E5">
-        <v>0.0131431335659312</v>
+        <v>0.01469545343013583</v>
       </c>
       <c r="F5">
-        <v>0.03747503252656583</v>
+        <v>0.03991805114759935</v>
       </c>
       <c r="G5">
-        <v>0.07734613415419576</v>
+        <v>0.07729542266160278</v>
       </c>
       <c r="H5">
-        <v>0.1177012803275683</v>
+        <v>0.1209152299127166</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -667,25 +667,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.3737972224686041</v>
+        <v>0.3737972224432388</v>
       </c>
       <c r="C7">
-        <v>0.4017916669466445</v>
+        <v>0.4017916669332979</v>
       </c>
       <c r="D7">
-        <v>0.4717777779801329</v>
+        <v>0.4717777778434692</v>
       </c>
       <c r="E7">
-        <v>0.5238333334965315</v>
+        <v>0.5238333333718422</v>
       </c>
       <c r="F7">
-        <v>0.5758888891139763</v>
+        <v>0.5758888889950312</v>
       </c>
       <c r="G7">
-        <v>0.6722222223352146</v>
+        <v>0.6722222221348015</v>
       </c>
       <c r="H7">
-        <v>0.7685555533921686</v>
+        <v>0.7685555523458636</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -719,25 +719,25 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.130698329530741</v>
+        <v>0.1306983295201064</v>
       </c>
       <c r="C9">
-        <v>0.1404865370849596</v>
+        <v>0.140486504941159</v>
       </c>
       <c r="D9">
-        <v>0.1649570733714923</v>
+        <v>0.1649569391113469</v>
       </c>
       <c r="E9">
-        <v>0.1700153746454325</v>
+        <v>0.1684630547356191</v>
       </c>
       <c r="F9">
-        <v>0.1638847189056927</v>
+        <v>0.1614417002401318</v>
       </c>
       <c r="G9">
-        <v>0.1576966009189568</v>
+        <v>0.1577473123371433</v>
       </c>
       <c r="H9">
-        <v>0.1510244375866423</v>
+        <v>0.1478104876093913</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -748,22 +748,22 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>1.992984203665515E-07</v>
+        <v>2.819449355213736E-07</v>
       </c>
       <c r="D10">
-        <v>1.901656800387107E-07</v>
+        <v>2.746850208119735E-07</v>
       </c>
       <c r="E10">
-        <v>1.742058205430127E-07</v>
+        <v>2.516692071787573E-07</v>
       </c>
       <c r="F10">
-        <v>1.33258995963512E-07</v>
+        <v>1.918255239215505E-07</v>
       </c>
       <c r="G10">
-        <v>1.228569488058123E-07</v>
+        <v>1.770746075524889E-07</v>
       </c>
       <c r="H10">
-        <v>4.390666397977641E-07</v>
+        <v>6.570955341193882E-07</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -849,25 +849,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>3.951806214211032</v>
+        <v>3.951806216656125</v>
       </c>
       <c r="C14">
-        <v>4.014594489828625</v>
+        <v>4.01459448781942</v>
       </c>
       <c r="D14">
-        <v>4.414206458093597</v>
+        <v>4.414206445884694</v>
       </c>
       <c r="E14">
-        <v>5.271555712058687</v>
+        <v>5.271555582527991</v>
       </c>
       <c r="F14">
-        <v>6.268542692731002</v>
+        <v>6.02263198769621</v>
       </c>
       <c r="G14">
-        <v>7.206936600855816</v>
+        <v>7.206936632038214</v>
       </c>
       <c r="H14">
-        <v>9.11054312984804</v>
+        <v>9.110543322738634</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -979,25 +979,25 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>8.72181537802678E-08</v>
+        <v>1.231042409826928E-07</v>
       </c>
       <c r="C19">
-        <v>9.198294553363392E-08</v>
+        <v>1.318474274163942E-07</v>
       </c>
       <c r="D19">
-        <v>2.485257161184936E-07</v>
+        <v>3.652777687954554E-07</v>
       </c>
       <c r="E19">
-        <v>1.322120091626596E-06</v>
+        <v>1.622286736630871E-06</v>
       </c>
       <c r="F19">
-        <v>8.074602311138525E-06</v>
+        <v>2.266502405037076E-05</v>
       </c>
       <c r="G19">
-        <v>8.739258715527812E-06</v>
+        <v>2.44005797391544E-05</v>
       </c>
       <c r="H19">
-        <v>9.537822930136805E-06</v>
+        <v>2.275376210348175E-05</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1031,25 +1031,25 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>6.977452302783867E-08</v>
+        <v>9.84833927893584E-08</v>
       </c>
       <c r="C21">
-        <v>7.358635642690716E-08</v>
+        <v>1.054779419331153E-07</v>
       </c>
       <c r="D21">
-        <v>1.98820572894795E-07</v>
+        <v>2.922222150363645E-07</v>
       </c>
       <c r="E21">
-        <v>1.057696073301277E-06</v>
+        <v>1.297829389304697E-06</v>
       </c>
       <c r="F21">
-        <v>6.459681848910818E-06</v>
+        <v>1.813201924029659E-05</v>
       </c>
       <c r="G21">
-        <v>6.991406972422254E-06</v>
+        <v>1.952046379132352E-05</v>
       </c>
       <c r="H21">
-        <v>7.630258344109448E-06</v>
+        <v>1.82030096827854E-05</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1060,22 +1060,22 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>0.107757966284243</v>
+        <v>0.1077579661326415</v>
       </c>
       <c r="D22">
-        <v>0.1077579662837586</v>
+        <v>0.1077579661382567</v>
       </c>
       <c r="E22">
-        <v>0.107757966341244</v>
+        <v>0.1077579662412733</v>
       </c>
       <c r="F22">
-        <v>0.107757966386509</v>
+        <v>0.1077579662757306</v>
       </c>
       <c r="G22">
-        <v>0.1077579663595743</v>
+        <v>0.1077579662350437</v>
       </c>
       <c r="H22">
-        <v>0.107757965332375</v>
+        <v>0.1077579647505064</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1083,25 +1083,25 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.1767387963081899</v>
+        <v>0.1767387962667604</v>
       </c>
       <c r="C23">
-        <v>0.1767387963443424</v>
+        <v>0.176738796319507</v>
       </c>
       <c r="D23">
-        <v>0.1767387963204129</v>
+        <v>0.1767387962850885</v>
       </c>
       <c r="E23">
-        <v>0.1767387962999863</v>
+        <v>0.1767387962544238</v>
       </c>
       <c r="F23">
-        <v>0.1767387962689713</v>
+        <v>0.1767387962080975</v>
       </c>
       <c r="G23">
-        <v>0.1767387962081919</v>
+        <v>0.1767387961174458</v>
       </c>
       <c r="H23">
-        <v>0.1767387951421902</v>
+        <v>0.1767387945758883</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1109,25 +1109,25 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>1.253711478177155E-08</v>
+        <v>1.843066671445866E-08</v>
       </c>
       <c r="C24">
-        <v>3.41663916538979E-07</v>
+        <v>4.8371332708543E-07</v>
       </c>
       <c r="D24">
-        <v>3.254027678002994E-07</v>
+        <v>4.702854058777903E-07</v>
       </c>
       <c r="E24">
-        <v>2.991863180547884E-07</v>
+        <v>4.325520842638464E-07</v>
       </c>
       <c r="F24">
-        <v>2.3121210713703E-07</v>
+        <v>3.33252983507562E-07</v>
       </c>
       <c r="G24">
-        <v>2.162404242628449E-07</v>
+        <v>3.121625846362727E-07</v>
       </c>
       <c r="H24">
-        <v>7.981482212945413E-07</v>
+        <v>1.192901518482261E-06</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1135,25 +1135,25 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>4.497227477835103E-09</v>
+        <v>6.611194630586085E-09</v>
       </c>
       <c r="C25">
-        <v>2.454904255092265E-09</v>
+        <v>3.6040237031498E-09</v>
       </c>
       <c r="D25">
-        <v>2.805614011828489E-09</v>
+        <v>4.14466371712394E-09</v>
       </c>
       <c r="E25">
-        <v>3.584763464909927E-09</v>
+        <v>5.296196326504113E-09</v>
       </c>
       <c r="F25">
-        <v>4.056584910183045E-09</v>
+        <v>5.991317514346094E-09</v>
       </c>
       <c r="G25">
-        <v>4.83521259839627E-09</v>
+        <v>7.145484899882713E-09</v>
       </c>
       <c r="H25">
-        <v>2.790101087143028E-08</v>
+        <v>4.118906762503382E-08</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1190,22 +1190,22 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>5.848889381004197E-09</v>
+        <v>8.442558425074114E-09</v>
       </c>
       <c r="D27">
-        <v>1.710084019329889E-08</v>
+        <v>2.483338893473573E-08</v>
       </c>
       <c r="E27">
-        <v>3.721744277217254E-08</v>
+        <v>5.476228405370485E-08</v>
       </c>
       <c r="F27">
-        <v>6.347576788933542E-08</v>
+        <v>9.515027600431015E-08</v>
       </c>
       <c r="G27">
-        <v>1.088907219587857E-07</v>
+        <v>1.639053907392388E-07</v>
       </c>
       <c r="H27">
-        <v>8.080033204733937E-07</v>
+        <v>1.572440956977924E-06</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1268,22 +1268,22 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>6.158966882879136E-09</v>
+        <v>8.737027277789742E-09</v>
       </c>
       <c r="D30">
-        <v>1.547652961673746E-08</v>
+        <v>2.213134888526733E-08</v>
       </c>
       <c r="E30">
-        <v>2.719504226737267E-08</v>
+        <v>3.817057979071882E-08</v>
       </c>
       <c r="F30">
-        <v>6.159778123964307E-08</v>
+        <v>8.168768828297539E-08</v>
       </c>
       <c r="G30">
-        <v>1.665460879144118E-07</v>
+        <v>2.225554668499712E-07</v>
       </c>
       <c r="H30">
-        <v>4.138707440674854E-05</v>
+        <v>4.798999525360513E-06</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1291,25 +1291,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.8427731268289501</v>
+        <v>0.7954872924139441</v>
       </c>
       <c r="C31">
-        <v>0.9848755539833518</v>
+        <v>0.9333947250795599</v>
       </c>
       <c r="D31">
-        <v>0.9848694175574144</v>
+        <v>0.9333955038237927</v>
       </c>
       <c r="E31">
-        <v>0.9858915732097713</v>
+        <v>0.9343331545930265</v>
       </c>
       <c r="F31">
-        <v>1.064094278752868</v>
+        <v>1.050538558021483</v>
       </c>
       <c r="G31">
-        <v>1.159820919305387</v>
+        <v>1.136600546494873</v>
       </c>
       <c r="H31">
-        <v>1.230773111470637</v>
+        <v>1.18182427486741</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1320,22 +1320,22 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>9.163224245342593E-09</v>
+        <v>1.340522684515879E-08</v>
       </c>
       <c r="D32">
-        <v>3.175727543303122E-08</v>
+        <v>4.887546886464809E-08</v>
       </c>
       <c r="E32">
-        <v>1.367113566194484E-07</v>
+        <v>2.730808971639596E-07</v>
       </c>
       <c r="F32">
-        <v>0.1146610547352193</v>
+        <v>0.3605717718678007</v>
       </c>
       <c r="G32">
-        <v>0.3605717739522354</v>
+        <v>0.3605717582519825</v>
       </c>
       <c r="H32">
-        <v>0.3605716034080227</v>
+        <v>0.3605715059736331</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1343,25 +1343,25 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.03965074084994093</v>
+        <v>0.03965073842256117</v>
       </c>
       <c r="C33">
-        <v>0.03965074166990974</v>
+        <v>0.03965073947396942</v>
       </c>
       <c r="D33">
-        <v>0.03965073556325022</v>
+        <v>0.03965073067211841</v>
       </c>
       <c r="E33">
-        <v>0.03965073121354661</v>
+        <v>0.03965072438720055</v>
       </c>
       <c r="F33">
-        <v>0.03965072155105416</v>
+        <v>0.03965070948318525</v>
       </c>
       <c r="G33">
-        <v>0.03965070700164578</v>
+        <v>0.0396506915503726</v>
       </c>
       <c r="H33">
-        <v>0.03965053810099601</v>
+        <v>0.03965044287893833</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="C34">
-        <v>6.62581673205451E-09</v>
+        <v>9.567228127625424E-09</v>
       </c>
       <c r="D34">
-        <v>7.910702131852257E-09</v>
+        <v>1.164204132841627E-08</v>
       </c>
       <c r="E34">
-        <v>1.297300580087354E-08</v>
+        <v>1.918300766785529E-08</v>
       </c>
       <c r="F34">
-        <v>1.907390968300003E-08</v>
+        <v>2.813096635203442E-08</v>
       </c>
       <c r="G34">
-        <v>2.703986975542E-08</v>
+        <v>4.02360225641232E-08</v>
       </c>
       <c r="H34">
-        <v>1.652281952921261E-07</v>
+        <v>2.549027073621212E-07</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1395,25 +1395,25 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>0.07388702913854503</v>
+        <v>0.073881355512707</v>
       </c>
       <c r="C35">
-        <v>0.0738886968499792</v>
+        <v>0.07388737199455728</v>
       </c>
       <c r="D35">
-        <v>0.07388819752512302</v>
+        <v>0.07388568695784296</v>
       </c>
       <c r="E35">
-        <v>0.07388738790104157</v>
+        <v>0.07388238106373315</v>
       </c>
       <c r="F35">
-        <v>0.07388670467841918</v>
+        <v>0.07388079105683404</v>
       </c>
       <c r="G35">
-        <v>0.07388540702755302</v>
+        <v>0.0738793362092779</v>
       </c>
       <c r="H35">
-        <v>0.07386359169801519</v>
+        <v>0.07353778784886569</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1424,22 +1424,22 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>2.33007295411768E-08</v>
+        <v>3.211074940268381E-08</v>
       </c>
       <c r="D36">
-        <v>2.667167969527906E-08</v>
+        <v>3.844235721515647E-08</v>
       </c>
       <c r="E36">
-        <v>5.008645382005116E-08</v>
+        <v>7.354234975695658E-08</v>
       </c>
       <c r="F36">
-        <v>6.259315404824391E-08</v>
+        <v>9.36584502175708E-08</v>
       </c>
       <c r="G36">
-        <v>7.447033956265882E-08</v>
+        <v>1.111858497885429E-07</v>
       </c>
       <c r="H36">
-        <v>3.999948170581377E-07</v>
+        <v>6.649860882539391E-07</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1447,25 +1447,25 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.03865741418674862</v>
+        <v>0.03743136762880092</v>
       </c>
       <c r="C37">
-        <v>0.04028803861260259</v>
+        <v>0.03953400224811586</v>
       </c>
       <c r="D37">
-        <v>0.03907098475544264</v>
+        <v>0.03848346064389921</v>
       </c>
       <c r="E37">
-        <v>0.03935641720444671</v>
+        <v>0.03881063944517889</v>
       </c>
       <c r="F37">
-        <v>0.04176567268224662</v>
+        <v>0.04133784615173788</v>
       </c>
       <c r="G37">
-        <v>0.04431827690477684</v>
+        <v>0.04358305737789742</v>
       </c>
       <c r="H37">
-        <v>0.04715907671415461</v>
+        <v>0.0447107545764184</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>0.5151394116051611</v>
+        <v>0.5636569686313324</v>
       </c>
       <c r="C38">
-        <v>0.3714047087775718</v>
+        <v>0.4236409089701359</v>
       </c>
       <c r="D38">
-        <v>0.3726284222401238</v>
+        <v>0.4246923919140432</v>
       </c>
       <c r="E38">
-        <v>0.3713216769263749</v>
+        <v>0.4234309175621829</v>
       </c>
       <c r="F38">
-        <v>0.2907104663713623</v>
+        <v>0.304699993919396</v>
       </c>
       <c r="G38">
-        <v>0.1924326435940944</v>
+        <v>0.2163944194187054</v>
       </c>
       <c r="H38">
-        <v>0.1186774684383666</v>
+        <v>0.1703884915603368</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1525,25 +1525,25 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>1.520893942433175E-07</v>
+        <v>2.162965443774541E-07</v>
       </c>
       <c r="C40">
-        <v>1.607074373916188E-07</v>
+        <v>2.304307340012495E-07</v>
       </c>
       <c r="D40">
-        <v>5.153708374365237E-07</v>
+        <v>7.620390538481226E-07</v>
       </c>
       <c r="E40">
-        <v>2.152976001225159E-06</v>
+        <v>2.704191812231462E-06</v>
       </c>
       <c r="F40">
-        <v>0.2446057629338472</v>
+        <v>0.2324935783105629</v>
       </c>
       <c r="G40">
-        <v>0.5783030488966481</v>
+        <v>0.7495949598821503</v>
       </c>
       <c r="H40">
-        <v>1.06904504895101</v>
+        <v>0.9716267788419729</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,25 +1551,25 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>1.249150774237835E-07</v>
+        <v>1.776968506769036E-07</v>
       </c>
       <c r="C41">
-        <v>1.32002174512687E-07</v>
+        <v>1.892737525346468E-07</v>
       </c>
       <c r="D41">
-        <v>4.256389260216444E-07</v>
+        <v>6.29469307335558E-07</v>
       </c>
       <c r="E41">
-        <v>1.763923596466656E-06</v>
+        <v>2.21744870356971E-06</v>
       </c>
       <c r="F41">
-        <v>0.2079144947636252</v>
+        <v>0.1976184083127505</v>
       </c>
       <c r="G41">
-        <v>0.4915571546000745</v>
+        <v>0.6371544958707936</v>
       </c>
       <c r="H41">
-        <v>0.9086878147169744</v>
+        <v>0.8258816243276232</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1577,25 +1577,25 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-2.717431681953406E-08</v>
+        <v>-3.859969370055044E-08</v>
       </c>
       <c r="C42">
-        <v>-2.870526287893177E-08</v>
+        <v>-4.115698146660272E-08</v>
       </c>
       <c r="D42">
-        <v>-8.973191141487927E-08</v>
+        <v>-1.325697465125646E-07</v>
       </c>
       <c r="E42">
-        <v>-3.890524047585035E-07</v>
+        <v>-4.867431086617513E-07</v>
       </c>
       <c r="F42">
-        <v>-0.036691268170222</v>
+        <v>-0.03487516999781248</v>
       </c>
       <c r="G42">
-        <v>-0.08674589429657353</v>
+        <v>-0.1124404640113567</v>
       </c>
       <c r="H42">
-        <v>-0.1603572342340356</v>
+        <v>-0.1457451545143497</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1603,25 +1603,25 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>2.769700647062104</v>
+        <v>2.818218213836087</v>
       </c>
       <c r="C43">
-        <v>2.572489125796201</v>
+        <v>2.62472522570002</v>
       </c>
       <c r="D43">
-        <v>2.957009505400909</v>
+        <v>3.009073369680049</v>
       </c>
       <c r="E43">
-        <v>3.812347915816118</v>
+        <v>3.864456947974476</v>
       </c>
       <c r="F43">
-        <v>4.767559888905668</v>
+        <v>4.528803809192393</v>
       </c>
       <c r="G43">
-        <v>5.64319822810073</v>
+        <v>5.692854276096964</v>
       </c>
       <c r="H43">
-        <v>7.551768330658867</v>
+        <v>7.588914649814917</v>
       </c>
     </row>
     <row r="44" spans="1:8">
